--- a/src/attributions/attributions_ig_traj_319.xlsx
+++ b/src/attributions/attributions_ig_traj_319.xlsx
@@ -1568,10 +1568,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6307830133055545</v>
+        <v>0.002684433984562604</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -1580,16 +1580,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1137854720572212</v>
+        <v>0.0009294644255395667</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1212063973579957</v>
+        <v>-0.0006983015022668797</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -1598,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.04649462220367228</v>
+        <v>-0.0003546857691233432</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1607,13 +1607,13 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00737109557255894</v>
+        <v>-9.770103094209682e-05</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01452723642026616</v>
+        <v>0.0002122532690541714</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1625,49 +1625,49 @@
         <v>-0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2981717562672801</v>
+        <v>-0.0002886932516119767</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2438930067243738</v>
+        <v>-0.001589424842435835</v>
       </c>
       <c r="X3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01188203271204389</v>
+        <v>0.0001593759442352801</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.284629193543439</v>
+        <v>-0.003052167290512669</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.1769428009876433</v>
+        <v>-0.001170964321911927</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.02974567802583148</v>
+        <v>-0.002205756574739235</v>
       </c>
       <c r="AI3" t="n">
         <v>-0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.2630408078678596</v>
+        <v>0.0004191796760498412</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1688,16 +1688,16 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1410614976687376</v>
+        <v>0.001935256613879948</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.06565140244472241</v>
+        <v>-0.0002874397876936738</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
@@ -1706,34 +1706,34 @@
         <v>-0</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.153570912877359</v>
+        <v>0.008455643085308742</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.3658280076687258</v>
+        <v>0.003062083089229406</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.3618581734768607</v>
+        <v>-0.0002132428488926816</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.03980501511107239</v>
+        <v>-0.0005107614270113381</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1742,16 +1742,16 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.1252533396313057</v>
+        <v>-0.0005266145914384557</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0273873862775735</v>
+        <v>-7.450794626020483e-05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
@@ -1760,22 +1760,22 @@
         <v>-0</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.3107315695136774</v>
+        <v>0.002069348991479325</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
         <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1377067358715378</v>
+        <v>0.005084054250669707</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1916405808360243</v>
+        <v>-0.0007018956184538942</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1787,49 +1787,49 @@
         <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.5707690535339038</v>
+        <v>0.003582364021048216</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.3584811118250953</v>
+        <v>0.001123381520155456</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.06445381498517941</v>
+        <v>-0.0002641777208428526</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.3429010276044209</v>
+        <v>-0.001214711228135179</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.03567443242445035</v>
+        <v>-0.00146415021272754</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.1343244793408382</v>
+        <v>0.0007947981723076714</v>
       </c>
       <c r="CK3" t="n">
         <v>-0</v>
@@ -1838,28 +1838,28 @@
         <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.002970991990547838</v>
+        <v>-0.000978520953151048</v>
       </c>
       <c r="CO3" t="n">
         <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.3762068523782481</v>
+        <v>-0.001538418884046558</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.03638932912266875</v>
+        <v>-0.00096454064861178</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
         <v>-0</v>
@@ -1868,22 +1868,22 @@
         <v>-0</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.3613120174206236</v>
+        <v>-0.001777866919964677</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.08720301102994747</v>
+        <v>-0.001343759492367338</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.1513357047615957</v>
+        <v>0.0009281935326884115</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,10 +1892,10 @@
         <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.3309364039092341</v>
+        <v>-0.004072731819649102</v>
       </c>
       <c r="DG3" t="n">
         <v>-0</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.2346110997204132</v>
+        <v>-0.005651674247766191</v>
       </c>
       <c r="DJ3" t="n">
         <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.08535407475023642</v>
+        <v>0.001045674263800275</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
@@ -1919,52 +1919,52 @@
         <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.13248302967384</v>
+        <v>-0.0002002410647791002</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.2555543262521704</v>
+        <v>-0.0002518205224287639</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.0752872163316558</v>
+        <v>0.003624417320596475</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.4166242972843223</v>
+        <v>-0.000130146878818939</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.1276109299063513</v>
+        <v>-0.00237469390512119</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.04684868928551229</v>
+        <v>0.003849431371809046</v>
       </c>
       <c r="ED3" t="n">
         <v>-0</v>
@@ -1976,22 +1976,22 @@
         <v>-0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.2403415734029576</v>
+        <v>-0.002673816443678011</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.077885614620022</v>
+        <v>-0.001864326460882844</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.2019606160594069</v>
+        <v>-0.0006202590014440069</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
@@ -2003,34 +2003,34 @@
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.221416947849722</v>
+        <v>-0.0002251377607326436</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER3" t="n">
         <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.1454848226210043</v>
+        <v>-0.001187152949498593</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.07808883184399931</v>
+        <v>0.003087434765863631</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.3797499465028073</v>
+        <v>-0.002314694353739375</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
@@ -2039,13 +2039,13 @@
         <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.1389737417046077</v>
+        <v>-0.00245975935685538</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.1535853223010761</v>
+        <v>0.001003358130081933</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
@@ -2054,10 +2054,10 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.01703578158650223</v>
+        <v>0.002789926499541888</v>
       </c>
       <c r="FI3" t="n">
         <v>-0</v>
@@ -2066,25 +2066,25 @@
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.195341288370843</v>
+        <v>-0.000219087922463278</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>-0.0103568657272283</v>
+        <v>-0.001071647065686724</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.05260610480226133</v>
+        <v>-5.53568671518759e-06</v>
       </c>
       <c r="FR3" t="n">
         <v>-0</v>
@@ -2093,25 +2093,25 @@
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.02004835364850027</v>
+        <v>0.0003264704609593761</v>
       </c>
       <c r="FU3" t="n">
         <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.09416707317976589</v>
+        <v>0.002508495355503221</v>
       </c>
       <c r="FW3" t="n">
         <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.1639165972838273</v>
+        <v>-0.002614298080612595</v>
       </c>
       <c r="GA3" t="n">
         <v>0</v>
@@ -2120,16 +2120,16 @@
         <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
-        <v>-0.2020212534064028</v>
+        <v>0.001775101957622648</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
         <v>-0</v>
@@ -2709,49 +2709,49 @@
         <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.6865085277384855</v>
+        <v>-0.3023541611464362</v>
       </c>
       <c r="C5" t="n">
         <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7671673113064909</v>
+        <v>0.306288635169367</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1502897971190082</v>
+        <v>-0.003398190076560388</v>
       </c>
       <c r="F5" t="n">
         <v>-0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>-0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01305109952160042</v>
+        <v>0.007893934379002043</v>
       </c>
       <c r="L5" t="n">
         <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0227501010723038</v>
+        <v>0.01255807893895983</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.002416996065639141</v>
+        <v>-5.069160701623535e-05</v>
       </c>
       <c r="O5" t="n">
         <v>-0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-0</v>
@@ -2763,22 +2763,22 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3282798509168379</v>
+        <v>-0.1664777478923188</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.08670181413581193</v>
+        <v>0.03575023141634408</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1907479403307571</v>
+        <v>-0.0002728735349574069</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
@@ -2787,46 +2787,46 @@
         <v>-0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.3389284215487919</v>
+        <v>0.2214823835369955</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.09051292821893984</v>
+        <v>0.4588914748727536</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1347474757229267</v>
+        <v>-0.05154799565110532</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK5" t="n">
         <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.386665076177764</v>
+        <v>-0.3177476245877115</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.2046625946541955</v>
+        <v>0.1572885770194695</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.04490212281133383</v>
+        <v>-0.3157628316533576</v>
       </c>
       <c r="AP5" t="n">
         <v>-0</v>
@@ -2844,19 +2844,19 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>-1.703958544067629</v>
+        <v>-0.8075805985841478</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.642634109567808</v>
+        <v>0.4455997781946013</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.1046556823114055</v>
+        <v>0.07736279396053471</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
         <v>-0</v>
@@ -2865,25 +2865,25 @@
         <v>-0</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
         <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-8.143417641898445e-11</v>
+        <v>5.015804478571345e-11</v>
       </c>
       <c r="BE5" t="n">
         <v>-0</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.1115464986700419</v>
+        <v>0.02465739424480199</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.1463856250954166</v>
+        <v>0.03102609227731423</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
@@ -2895,46 +2895,46 @@
         <v>-0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.394930895304933</v>
+        <v>0.2572259954440478</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.09796955983364329</v>
+        <v>-0.02805371729534365</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.2066526582586385</v>
+        <v>0.01134957625336947</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU5" t="n">
         <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.8871178954885434</v>
+        <v>-0.6045913414718956</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.4034108906647306</v>
+        <v>0.2389433874685183</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.2028070654945834</v>
+        <v>-0.004141617169620962</v>
       </c>
       <c r="BZ5" t="n">
         <v>-0</v>
@@ -2943,55 +2943,55 @@
         <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD5" t="n">
         <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.3970731405213271</v>
+        <v>0.3378896662632922</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.2080434058258332</v>
+        <v>-0.2398138007014187</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.09215437270741078</v>
+        <v>0.02377644823722819</v>
       </c>
       <c r="CI5" t="n">
         <v>0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
         <v>-0</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM5" t="n">
         <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.2489278079478302</v>
+        <v>0.1010228724765557</v>
       </c>
       <c r="CO5" t="n">
         <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.2849380566679569</v>
+        <v>-0.4274553817489546</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.2110533114456414</v>
+        <v>-0.1795553951364831</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS5" t="n">
         <v>0</v>
@@ -3000,49 +3000,49 @@
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.4185013512052779</v>
+        <v>0.3577288373656841</v>
       </c>
       <c r="CX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.2960825175659798</v>
+        <v>-0.254335708858566</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.05904399745025574</v>
+        <v>-0.01841991162612403</v>
       </c>
       <c r="DA5" t="n">
         <v>-0</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
       </c>
       <c r="DD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE5" t="n">
         <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.6440743776658021</v>
+        <v>0.4743299844712607</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.08087683298450681</v>
+        <v>-0.1320728254489908</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.09359585188777024</v>
+        <v>-0.01180234686639284</v>
       </c>
       <c r="DJ5" t="n">
         <v>0</v>
@@ -3054,28 +3054,28 @@
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.07202348270466813</v>
+        <v>0.0689570368059165</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.02643842161879199</v>
+        <v>-0.0470580384022633</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.2009488980433888</v>
+        <v>0.02951256855148422</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
@@ -3084,28 +3084,28 @@
         <v>-0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.2152066559603375</v>
+        <v>-0.1335260454009177</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.07277068977342423</v>
+        <v>0.1217038330646579</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.2188962902367441</v>
+        <v>0.2016099963856508</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE5" t="n">
         <v>0</v>
@@ -3114,25 +3114,25 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.4110206387045223</v>
+        <v>0.3094794242663214</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.08533769411109808</v>
+        <v>-0.1975040103586561</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.2479976820266469</v>
+        <v>-0.08218666688940292</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
         <v>0</v>
@@ -3141,22 +3141,22 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.3987457081056032</v>
+        <v>0.1606238608481291</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.3839903375653442</v>
+        <v>-0.1608437251353318</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.1435947014504796</v>
+        <v>0.03636236068938609</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
         <v>-0</v>
@@ -3165,76 +3165,76 @@
         <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.4525494413643148</v>
+        <v>0.357049807864384</v>
       </c>
       <c r="EZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA5" t="n">
-        <v>-0.2551351920339113</v>
+        <v>-0.2837684102120055</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.164833692212381</v>
+        <v>0.03814948538117575</v>
       </c>
       <c r="FC5" t="n">
         <v>0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
       </c>
       <c r="FF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG5" t="n">
         <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.1819118236371616</v>
+        <v>0.307088645843933</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.3339673596883868</v>
+        <v>-0.2234376295241781</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.2534054900454376</v>
+        <v>0.00328399874443561</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.05497878800955967</v>
+        <v>0.07250023340005392</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>-0.3129336889351532</v>
+        <v>-0.186203296585066</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.01951719417388581</v>
+        <v>-0.004844007347303296</v>
       </c>
       <c r="FU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV5" t="n">
         <v>0</v>
@@ -3246,28 +3246,28 @@
         <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.05374496499568995</v>
+        <v>0.4748494607517587</v>
       </c>
       <c r="GA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.09705909773797958</v>
+        <v>-0.1444074744904037</v>
       </c>
       <c r="GC5" t="n">
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE5" t="n">
         <v>0</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -3278,43 +3278,43 @@
         <v>-0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5612517072079306</v>
+        <v>0.3245595510569579</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2367072674587111</v>
+        <v>-0.08870736183679004</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.05690861260242547</v>
+        <v>-0.01322056581460113</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>-0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05922514328558327</v>
+        <v>0.04201086765342842</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0758696788509929</v>
+        <v>0.05415773264038459</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.003357929726345081</v>
+        <v>-0.0009142236157672796</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3332,70 +3332,70 @@
         <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.132023825231223</v>
+        <v>0.08125766058008832</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.01219233796618984</v>
+        <v>0.0387470790848196</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01434675376505924</v>
+        <v>0.0575282394754472</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1195214110864614</v>
+        <v>-0.0103513310641877</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.03790168286089422</v>
+        <v>-0.1119075005223077</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1536960049940838</v>
+        <v>-0.02084129495817017</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.1187359306337981</v>
+        <v>0.1716827457986822</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.0836650328490743</v>
+        <v>0.02407844904619859</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.2092796714786555</v>
+        <v>0.1341803414274642</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
@@ -3404,52 +3404,52 @@
         <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.8249227375327709</v>
+        <v>0.4060057158261173</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.3972600136451407</v>
+        <v>-0.1654418222845709</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1893054164242115</v>
+        <v>-0.03836216889445912</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB6" t="n">
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.06483343699569269</v>
+        <v>0.002006986519908887</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.07102986481368438</v>
+        <v>-0.01677494351538632</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.03788566405042044</v>
+        <v>-0.01248907481463807</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -3458,28 +3458,28 @@
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.01268370479412346</v>
+        <v>-0.09712520031046315</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0386484885326218</v>
+        <v>0.04416388227534277</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.3057631168653159</v>
+        <v>0.07294649237087591</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
@@ -3494,22 +3494,22 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.418870837735645</v>
+        <v>0.3411746443646449</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.06764663714034357</v>
+        <v>-0.03818468305094916</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.05302198802955849</v>
+        <v>0.1012019541669634</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,46 +3521,46 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.1677883773606476</v>
+        <v>-0.1745025717979703</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.1701237361733873</v>
+        <v>0.1229597837818864</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.05184549500215233</v>
+        <v>-0.02060684960506966</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ6" t="n">
         <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.005591918083767505</v>
+        <v>-0.1546118653984856</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.1918587110354624</v>
+        <v>0.1145104591853643</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.359605919173731</v>
+        <v>-0.05967756848897163</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
@@ -3572,19 +3572,19 @@
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.1789721938049169</v>
+        <v>-0.1939516163450982</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.2000544202585205</v>
+        <v>0.1142832364424181</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.04085023269022525</v>
+        <v>-0.01137715320008156</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
@@ -3596,25 +3596,25 @@
         <v>0</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.2733480682211984</v>
+        <v>-0.1936488802733439</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.4101932791269873</v>
+        <v>0.1381344255388941</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0001689665890014796</v>
+        <v>-0.03134503686921467</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3626,76 +3626,76 @@
         <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.162789880831287</v>
+        <v>-0.09201942681441809</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.1160095292081591</v>
+        <v>0.05058345395523253</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.0486634600812138</v>
+        <v>-0.0475112730400853</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.1661309999430051</v>
+        <v>0.08193200782242722</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.01396173134387646</v>
+        <v>0.09432024160048909</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.0365683202580817</v>
+        <v>0.006087661895365109</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
         <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.1856983285942256</v>
+        <v>-0.1196471785098629</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.4478055939785484</v>
+        <v>-0.2101072778379145</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.09798098004553829</v>
+        <v>-0.004059161278588552</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
@@ -3710,46 +3710,46 @@
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.1528028721656787</v>
+        <v>-0.130284934689197</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.1683671365013918</v>
+        <v>0.03338327995467849</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.1065444186444907</v>
+        <v>-0.04434671160616506</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
         <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.1878195970013871</v>
+        <v>-0.1965973387940558</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.1931748746045271</v>
+        <v>0.1377010614378538</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.04944479951741659</v>
+        <v>-0.02928726197382202</v>
       </c>
       <c r="FC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD6" t="n">
         <v>-0</v>
@@ -3758,49 +3758,49 @@
         <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.1031428729346771</v>
+        <v>-0.08728042764151532</v>
       </c>
       <c r="FI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.04302535922477749</v>
+        <v>-0.04213173043584535</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.03144418475955625</v>
+        <v>0.02879169911754803</v>
       </c>
       <c r="FL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN6" t="n">
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.05305569743433073</v>
+        <v>-0.1606916200945149</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
       </c>
       <c r="FS6" t="n">
-        <v>-0.03410918798431225</v>
+        <v>0.1883093697372808</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.255457961427902</v>
+        <v>0.03399790165692672</v>
       </c>
       <c r="FU6" t="n">
         <v>0</v>
@@ -3815,22 +3815,22 @@
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.04454727541507415</v>
+        <v>-0.1522017261117001</v>
       </c>
       <c r="GA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.03397746197965999</v>
+        <v>0.0204742435118579</v>
       </c>
       <c r="GC6" t="n">
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -3844,25 +3844,25 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.06596495065926718</v>
+        <v>-0.08682528235940355</v>
       </c>
       <c r="B7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2539374967827356</v>
+        <v>0.119351254408857</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2172531623971761</v>
+        <v>-0.1107069280362988</v>
       </c>
       <c r="F7" t="n">
         <v>-0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005064227411030432</v>
+        <v>-0.0008775067512656952</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -3871,187 +3871,187 @@
         <v>-0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0006890056125137216</v>
+        <v>-0.01803215646556505</v>
       </c>
       <c r="K7" t="n">
         <v>-0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02373199288147149</v>
+        <v>0.01317574976928553</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02107656414128677</v>
+        <v>-0.01937450307595142</v>
       </c>
       <c r="O7" t="n">
         <v>-0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0001320463575392337</v>
+        <v>-0.0007500645416179988</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.009378240259440064</v>
+        <v>-0.0226824601316443</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03622953471075113</v>
+        <v>-0.006713615663146929</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06543785706396733</v>
+        <v>-0.05422085926995888</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001440699604320293</v>
+        <v>0.01291979347689969</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.03876702726351169</v>
+        <v>0.1490883337651705</v>
       </c>
       <c r="AC7" t="n">
         <v>-0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.01523846433939323</v>
+        <v>-0.09243144883112304</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.1008860372393822</v>
+        <v>-0.1115462499902323</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.07975805001047838</v>
+        <v>0.04952533239108016</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.005574765841774045</v>
+        <v>-0.01584823682360419</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.04859177902567104</v>
+        <v>-0.01647923009901311</v>
       </c>
       <c r="AN7" t="n">
         <v>-0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02768967967971995</v>
+        <v>-0.04599702303320991</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.05258627370814305</v>
+        <v>0.04037606508543762</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.03038616151354694</v>
+        <v>-0.121754095636292</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.4072457101498411</v>
+        <v>0.1001365373718664</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.6123125244989408</v>
+        <v>-0.1786410910460628</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.2295878230715977</v>
+        <v>0.007020215604306457</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.0651610044282652</v>
+        <v>0.002203089362507736</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.0077482234452472</v>
+        <v>-0.003522978000376641</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.03725556410243235</v>
+        <v>0.002413909037719231</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.02097006825493407</v>
+        <v>-0.01441477031898214</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.05458209030750746</v>
+        <v>0.05039620645866878</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0776822141658062</v>
+        <v>0.01248226902431427</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1429026396722899</v>
+        <v>0.03381912918975487</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.09358094242249401</v>
+        <v>0.06718999096435414</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4060,52 +4060,52 @@
         <v>-0</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.004366114518995902</v>
+        <v>-0.0348582476254166</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.1818801636715014</v>
+        <v>0.1022114864797365</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.3330504781116913</v>
+        <v>-0.1285558299465174</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.04160386606028341</v>
+        <v>0.00783417904158875</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>-0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.01324871866760038</v>
+        <v>0.03151346368726038</v>
       </c>
       <c r="CE7" t="n">
         <v>-0</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.05382220616046946</v>
+        <v>-0.01529629135598346</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.06316887616325863</v>
+        <v>0.0830321792184827</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.003871946801658752</v>
+        <v>0.002819997962281776</v>
       </c>
       <c r="CK7" t="n">
         <v>-0</v>
@@ -4114,160 +4114,160 @@
         <v>-0</v>
       </c>
       <c r="CM7" t="n">
-        <v>-0.04655211952749864</v>
+        <v>-0.1069233650034323</v>
       </c>
       <c r="CN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.06628961109042522</v>
+        <v>0.044876375428701</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.4295054240565387</v>
+        <v>0.004318346187723215</v>
       </c>
       <c r="CR7" t="n">
         <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.1326371351517017</v>
+        <v>0.0256199291705239</v>
       </c>
       <c r="CT7" t="n">
         <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0.01462016631315086</v>
+        <v>0.04005799281838096</v>
       </c>
       <c r="CW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0.05598685087227507</v>
+        <v>-0.04259527366198551</v>
       </c>
       <c r="CY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.05169801661830114</v>
+        <v>0.04391107462200183</v>
       </c>
       <c r="DA7" t="n">
         <v>-0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.008617241874832066</v>
+        <v>0.02177674057859222</v>
       </c>
       <c r="DC7" t="n">
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.08559695251575425</v>
+        <v>0.01448023482115228</v>
       </c>
       <c r="DF7" t="n">
         <v>0</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0.0542488171143944</v>
+        <v>-0.04614203699763306</v>
       </c>
       <c r="DH7" t="n">
         <v>-0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.07870398211305159</v>
+        <v>0.1423683601949788</v>
       </c>
       <c r="DJ7" t="n">
         <v>0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0.03511934813055043</v>
+        <v>-0.02910376459674479</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
         <v>-0</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.1123497713003989</v>
+        <v>-0.1169804528076234</v>
       </c>
       <c r="DO7" t="n">
         <v>-0</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0.0255920453073697</v>
+        <v>0.02120459077526372</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.02263216936398301</v>
+        <v>-0.1622109630791232</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.01126287849718611</v>
+        <v>0.01304112881123768</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-0.01925154809839605</v>
+        <v>0.0270921653336081</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.06224262681456037</v>
+        <v>0.07068042978044797</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.2080674572619265</v>
+        <v>-0.1240995230061736</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
       </c>
       <c r="EC7" t="n">
-        <v>-0.05547878923276085</v>
+        <v>-0.02745484055882145</v>
       </c>
       <c r="ED7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE7" t="n">
         <v>0</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0.03555824703492624</v>
+        <v>0.04335692920809976</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH7" t="n">
-        <v>-0.1139234113367323</v>
+        <v>-0.01780542012009407</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.06141019274701472</v>
+        <v>0.05711377773625831</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0.04615486951175594</v>
+        <v>0.05097969326348812</v>
       </c>
       <c r="EM7" t="n">
         <v>-0</v>
@@ -4276,139 +4276,139 @@
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.1394379728258448</v>
+        <v>0.05931162677547422</v>
       </c>
       <c r="EP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0.01812550962820374</v>
+        <v>0.0222215866315992</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.2103041183070886</v>
+        <v>0.09159255709515012</v>
       </c>
       <c r="ET7" t="n">
         <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0.1114209317131596</v>
+        <v>0.0667322781027405</v>
       </c>
       <c r="EV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0.0106003043603052</v>
+        <v>0.04227109732688007</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ7" t="n">
-        <v>-0.0483102309671113</v>
+        <v>-0.04060825998460282</v>
       </c>
       <c r="FA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.04242526012600149</v>
+        <v>0.07172561482414042</v>
       </c>
       <c r="FC7" t="n">
         <v>0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0.01012693694011217</v>
+        <v>-0.002477394123621465</v>
       </c>
       <c r="FE7" t="n">
         <v>-0</v>
       </c>
       <c r="FF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.09876196970635691</v>
+        <v>0.2173920052362768</v>
       </c>
       <c r="FH7" t="n">
         <v>0</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0.06852076650697403</v>
+        <v>-0.02515219184886977</v>
       </c>
       <c r="FJ7" t="n">
         <v>0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.08240400143774661</v>
+        <v>0.06223717560761436</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0.1778840217146625</v>
+        <v>0.04915627999955677</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.1152827145519482</v>
+        <v>0.1918919367671639</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.05721879728000898</v>
+        <v>-0.1068365529902545</v>
       </c>
       <c r="FS7" t="n">
         <v>0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.02036436487947244</v>
+        <v>0.1217945772820266</v>
       </c>
       <c r="FU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0.2035690260477959</v>
+        <v>0.001809783033635419</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.01875090481225128</v>
+        <v>0.08754820468078822</v>
       </c>
       <c r="FZ7" t="n">
         <v>-0</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.0961767284601401</v>
+        <v>-0.02967532269675451</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
-        <v>-0.1267270076182554</v>
+        <v>0.04282720649611923</v>
       </c>
       <c r="GF7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4416,25 +4416,25 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.08696240156983921</v>
+        <v>0.5281656959034464</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01731361992616592</v>
+        <v>0.1116806156316556</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.06954796910455054</v>
+        <v>-0.2937768770477889</v>
       </c>
       <c r="G8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4443,52 +4443,52 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0184867951896945</v>
+        <v>0.1772786485187926</v>
       </c>
       <c r="L8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.002716519263048792</v>
+        <v>-0.007018764388266334</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009129456448237655</v>
+        <v>0.004487923887024258</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001218885473475195</v>
+        <v>0.04962348575671057</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0233553525514248</v>
+        <v>-0.04399238244287605</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.002797837293870474</v>
+        <v>-0.05043412262440494</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -4497,160 +4497,160 @@
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.00756372710224291</v>
+        <v>0.08439502731330406</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.02322308041325812</v>
+        <v>-0.1476237916455069</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.007023614909762336</v>
+        <v>0.07559337621404248</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01357988103943641</v>
+        <v>0.1893704434583371</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.002931606364376383</v>
+        <v>0.1115370960034087</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.04285315088719167</v>
+        <v>-0.1924536877938864</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.09314149380144533</v>
+        <v>0.8445466808758187</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.01425275628103752</v>
+        <v>-0.322861244269892</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.0635720411149288</v>
+        <v>-0.3241446830630472</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.02069776785417756</v>
+        <v>0.01615681131740879</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.01534550384976635</v>
+        <v>0.04166864040648102</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.01244063093362886</v>
+        <v>-0.06472445645178539</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
         <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.03690970665248082</v>
+        <v>0.06545758505450708</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0003817730660428436</v>
+        <v>0.1485442492003262</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01526826853534006</v>
+        <v>0.1685471827699757</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.05042370949755173</v>
+        <v>0.5408591883236662</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.004725514264347272</v>
+        <v>0.03019211670235639</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.0164540810861443</v>
+        <v>-0.2862573563027829</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC8" t="n">
         <v>0</v>
@@ -4659,79 +4659,79 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.0215473279015567</v>
+        <v>-0.3193430100153254</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001166481975519713</v>
+        <v>-0.03961272192003638</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.03197932958283167</v>
+        <v>0.2281116716697324</v>
       </c>
       <c r="CJ8" t="n">
         <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.01426569860395813</v>
+        <v>-0.4525529539368244</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
         <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.01127009673830396</v>
+        <v>0.04462471763347353</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.02018614634432413</v>
+        <v>0.2169905039803631</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.01643195030832276</v>
+        <v>-0.3123439158238912</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.001283678286506492</v>
+        <v>-0.07721945050758128</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.03906657131468847</v>
+        <v>0.2128747849744066</v>
       </c>
       <c r="DB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD8" t="n">
         <v>0</v>
@@ -4740,61 +4740,61 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.003674238986659072</v>
+        <v>-0.04954227311003563</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01364978380863715</v>
+        <v>-0.05415953356908269</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.007284891781154905</v>
+        <v>0.1342953709611549</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.0009306954130474198</v>
+        <v>-0.1731203014981875</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.03832836545317418</v>
+        <v>0.01029427838448558</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0122036165260014</v>
+        <v>0.1176958509710202</v>
       </c>
       <c r="DT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.002765974657081912</v>
+        <v>0.240452598860751</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
@@ -4803,16 +4803,16 @@
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01593392536954518</v>
+        <v>-0.1059290744563497</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.001401982496032884</v>
+        <v>-0.1683168584202561</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
         <v>-0</v>
@@ -4821,7 +4821,7 @@
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.01529458603975213</v>
+        <v>-0.05435145699274935</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
@@ -4830,13 +4830,13 @@
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>-0.002724046881581673</v>
+        <v>-0.1717644135707545</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.02489492542695081</v>
+        <v>0.1095892319064162</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM8" t="n">
         <v>-0</v>
@@ -4845,28 +4845,28 @@
         <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.02186314946749723</v>
+        <v>-0.1424164354634693</v>
       </c>
       <c r="EQ8" t="n">
         <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.006333678343115123</v>
+        <v>-0.1730344884169388</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.03023856024828426</v>
+        <v>-0.02366571795643371</v>
       </c>
       <c r="EU8" t="n">
         <v>0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
         <v>0</v>
@@ -4875,34 +4875,34 @@
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.01840243294590506</v>
+        <v>-0.3209077727888594</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.003919387789580353</v>
+        <v>-0.1164926734728695</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.03577974053258065</v>
+        <v>0.1839125525596312</v>
       </c>
       <c r="FD8" t="n">
         <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.01366106361411641</v>
+        <v>-0.1790238160610123</v>
       </c>
       <c r="FI8" t="n">
         <v>0</v>
@@ -4911,37 +4911,37 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.02597536768675237</v>
+        <v>-0.05051113788874966</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.02294932343640471</v>
+        <v>0.2289505439731969</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.007345270851111301</v>
+        <v>-0.1043520282128313</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.009248753259162884</v>
+        <v>-0.03399980822745015</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0004631468097664364</v>
+        <v>0.001833584127843375</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
@@ -4950,31 +4950,31 @@
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.02429685326407507</v>
+        <v>-0.1272922210527945</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.01011781974559094</v>
+        <v>0.1241948321790447</v>
       </c>
       <c r="GE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG8" t="n">
         <v>0</v>
@@ -4985,16 +4985,16 @@
         <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.547536452357312</v>
+        <v>-0.5457196650884054</v>
       </c>
       <c r="C9" t="n">
         <v>-0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4229969525609661</v>
+        <v>0.4107180434865164</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06826763750932799</v>
+        <v>-0.0320540020252096</v>
       </c>
       <c r="F9" t="n">
         <v>-0</v>
@@ -5012,19 +5012,19 @@
         <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.11804636757738</v>
+        <v>-0.1637483430859588</v>
       </c>
       <c r="L9" t="n">
         <v>-0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1450033920258753</v>
+        <v>0.2031707134306045</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03125678605072967</v>
+        <v>-0.005932979708433234</v>
       </c>
       <c r="O9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -5033,58 +5033,58 @@
         <v>-0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1215252397157671</v>
+        <v>-0.03293052810119378</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1108848442279678</v>
+        <v>0.02615898758835906</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0160359785377091</v>
+        <v>-0.01743409835591378</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>-0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.1200536597693607</v>
+        <v>-0.03912465324989785</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.01118397436199644</v>
+        <v>0.04678410913178788</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.02019273564135845</v>
+        <v>-0.1492299700225835</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
         <v>-0</v>
@@ -5093,16 +5093,16 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.1456834126647889</v>
+        <v>-0.3290524843135549</v>
       </c>
       <c r="AM9" t="n">
         <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.1116914519563638</v>
+        <v>0.05486862629031894</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.1269596472516733</v>
+        <v>-0.376288010888136</v>
       </c>
       <c r="AP9" t="n">
         <v>-0</v>
@@ -5111,28 +5111,28 @@
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
         <v>-0</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.5267422695402201</v>
+        <v>-0.4496782287510067</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.3293351443559449</v>
+        <v>0.2068467193503369</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0245353126726451</v>
+        <v>-0.007547383367934136</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
         <v>-0</v>
@@ -5141,22 +5141,22 @@
         <v>-0</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.05280693561083062</v>
+        <v>-0.04208245924275023</v>
       </c>
       <c r="BE9" t="n">
         <v>-0</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.04020602871945585</v>
+        <v>0.01331621691850333</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.07191956941435235</v>
+        <v>0.0008642214717937082</v>
       </c>
       <c r="BH9" t="n">
         <v>-0</v>
@@ -5174,22 +5174,22 @@
         <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>-0.03547839558889505</v>
+        <v>0.1906629849034809</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>-0.1345848849876933</v>
+        <v>-0.09553374879115845</v>
       </c>
       <c r="BP9" t="n">
-        <v>-0.1080230732057737</v>
+        <v>0.06495014785040765</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS9" t="n">
         <v>0</v>
@@ -5201,16 +5201,16 @@
         <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>-0.4156453465925728</v>
+        <v>-0.4467331578771233</v>
       </c>
       <c r="BW9" t="n">
         <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.2647598681971799</v>
+        <v>0.2814483367634531</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.02427701501964301</v>
+        <v>-0.1719629424395923</v>
       </c>
       <c r="BZ9" t="n">
         <v>-0</v>
@@ -5228,16 +5228,16 @@
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.129904499760704</v>
+        <v>0.3835988716279848</v>
       </c>
       <c r="CF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0.1019576086317599</v>
+        <v>-0.24307542563902</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.03847736604543436</v>
+        <v>0.09066341956152218</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
@@ -5246,28 +5246,28 @@
         <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
         <v>-0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.03021549247835211</v>
+        <v>0.3788118473447046</v>
       </c>
       <c r="CO9" t="n">
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.1236441814655634</v>
+        <v>-0.2980207719977165</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.2355964694819475</v>
+        <v>0.1741550825137216</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS9" t="n">
         <v>0</v>
@@ -5276,22 +5276,22 @@
         <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV9" t="n">
         <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.153522393898556</v>
+        <v>0.3736402605679572</v>
       </c>
       <c r="CX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY9" t="n">
-        <v>-0.1264809555925134</v>
+        <v>-0.2259056036232523</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.03535572155583987</v>
+        <v>0.05121085773532225</v>
       </c>
       <c r="DA9" t="n">
         <v>-0</v>
@@ -5303,25 +5303,25 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.06636459318879355</v>
+        <v>0.01498363429770252</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0.179151679368873</v>
+        <v>-0.04018937712639504</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.007037525581287837</v>
+        <v>0.04853016063977204</v>
       </c>
       <c r="DJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
@@ -5333,19 +5333,19 @@
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.09943180555560621</v>
+        <v>0.2156614688857288</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.01655586822293811</v>
+        <v>-0.1636737734299462</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.08908554600377144</v>
+        <v>0.03331724431497225</v>
       </c>
       <c r="DS9" t="n">
         <v>-0</v>
@@ -5363,52 +5363,52 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.1767767077942589</v>
+        <v>0.2508481849597337</v>
       </c>
       <c r="DY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.06492267978911337</v>
+        <v>0.1671299005831074</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.03621404398348074</v>
+        <v>0.02934198351719694</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE9" t="n">
         <v>0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.06547135588333877</v>
+        <v>0.2646518816863817</v>
       </c>
       <c r="EH9" t="n">
         <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0.1131474177949861</v>
+        <v>-0.2297971409717142</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.05730911961655646</v>
+        <v>0.0121635850814012</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.1752777147956995</v>
+        <v>0.339066269417799</v>
       </c>
       <c r="EQ9" t="n">
         <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.07027144126651125</v>
+        <v>-0.1335937709885553</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.03077373592656375</v>
+        <v>-0.1365827545016361</v>
       </c>
       <c r="ET9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
         <v>-0</v>
@@ -5444,70 +5444,70 @@
         <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.147761222450078</v>
+        <v>0.3998283915643955</v>
       </c>
       <c r="EZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0.1264457961036675</v>
+        <v>-0.2742674392389964</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.05764027470398709</v>
+        <v>0.07631366252050391</v>
       </c>
       <c r="FC9" t="n">
         <v>0</v>
       </c>
       <c r="FD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE9" t="n">
         <v>-0</v>
       </c>
       <c r="FF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.1169394360009532</v>
+        <v>0.05356272290542063</v>
       </c>
       <c r="FI9" t="n">
         <v>0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>-0.09756166718123793</v>
+        <v>-0.03160206808626044</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.01811199059837642</v>
+        <v>0.3845110969466012</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
         <v>0</v>
       </c>
       <c r="FO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP9" t="n">
         <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.05046600644604425</v>
+        <v>-0.0112344370973818</v>
       </c>
       <c r="FR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.04299459517562762</v>
+        <v>0.04510155372756511</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0711530881802369</v>
+        <v>0.07042125305862844</v>
       </c>
       <c r="FU9" t="n">
         <v>0</v>
@@ -5516,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
         <v>-0</v>
@@ -5525,28 +5525,28 @@
         <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.02126345636744046</v>
+        <v>0.2594422896249713</v>
       </c>
       <c r="GA9" t="n">
         <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.02710973021421805</v>
+        <v>-0.3610876226068698</v>
       </c>
       <c r="GC9" t="n">
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE9" t="n">
         <v>0</v>
       </c>
       <c r="GF9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,73 +5554,73 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3017656482574297</v>
+        <v>0.2183539451476497</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.07990930653393963</v>
+        <v>-0.08784651724961051</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.02654266565282948</v>
+        <v>-0.02669976072399244</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.08347348576049204</v>
+        <v>0.09256368865195201</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.006227333897861984</v>
+        <v>-0.008366293393501024</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.01555403073214295</v>
+        <v>-0.02519800934203897</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.09093443021960643</v>
+        <v>0.03597822020275677</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.01874267695440963</v>
+        <v>-0.0191633078859368</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01589974757612766</v>
+        <v>-0.04848238453132938</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
@@ -5632,55 +5632,55 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.03869440976836925</v>
+        <v>-0.02364616462448322</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.01592635975434656</v>
+        <v>-0.06672735274123018</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.02295562794138831</v>
+        <v>-0.08482669189565932</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.03316420104703968</v>
+        <v>0.09672731601102678</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.0551712126526865</v>
+        <v>-0.01496636747527096</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.05071571855858059</v>
+        <v>0.06902906317050309</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,16 +5689,16 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.3759742722037662</v>
+        <v>0.2600998482446124</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.01914177744079298</v>
+        <v>-0.03596167475866113</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.09262518626204748</v>
+        <v>-0.1210813579162695</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.006142377567785751</v>
+        <v>-0.009255497649392135</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.03183730670170884</v>
+        <v>0.0007326529704474172</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.05135140265027405</v>
+        <v>-0.01332743472288633</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,31 +5734,31 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.05467811713358755</v>
+        <v>-0.01288935888933821</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0454925134240363</v>
+        <v>0.0002766741090503657</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1177224106244065</v>
+        <v>0.06481382805165756</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,19 +5770,19 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1960066316380888</v>
+        <v>0.1873305495140359</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.02166843389483894</v>
+        <v>-0.09163820734764255</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0337049356269357</v>
+        <v>-0.02455882335296199</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
@@ -5791,25 +5791,25 @@
         <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.08066729636694167</v>
+        <v>-0.09423190516313289</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.008972519369115433</v>
+        <v>0.06362472377938948</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.01535078414867847</v>
+        <v>0.01551393014464244</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ10" t="n">
         <v>-0</v>
@@ -5818,58 +5818,58 @@
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.02215183954925417</v>
+        <v>-0.07794031967236188</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.06066607291819601</v>
+        <v>0.08953751782941237</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.09967332353897548</v>
+        <v>0.03781624145055152</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.07117243338240935</v>
+        <v>-0.09247519144274637</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.02248849534178899</v>
+        <v>0.06730108521059515</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.01489478581314506</v>
+        <v>0.01442014679096143</v>
       </c>
       <c r="DA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB10" t="n">
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD10" t="n">
         <v>0</v>
@@ -5878,22 +5878,22 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.003741794435929306</v>
+        <v>0.003112174815130873</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.01871409537674262</v>
+        <v>0.0150511781156988</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.03702391390006553</v>
+        <v>-0.03866478860418437</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5905,151 +5905,151 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.04885650802916838</v>
+        <v>-0.05791891649557802</v>
       </c>
       <c r="DP10" t="n">
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.01446766111850815</v>
+        <v>-0.01176024178873872</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.03316953437169993</v>
+        <v>-0.007207854064189963</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0438489188304958</v>
+        <v>0.08393436212077429</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.001149955514790745</v>
+        <v>0.03594064270488417</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.05687772426192475</v>
+        <v>-0.07454503663860224</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
         <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.06911683363151017</v>
+        <v>-0.0495870797112623</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.02299052186341357</v>
+        <v>0.05856435820876767</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.02988402928089696</v>
+        <v>0.01698095629039901</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.05176796436357432</v>
+        <v>-0.03986683437926694</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.03111458654780713</v>
+        <v>0.05452924840971168</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.007250029016247001</v>
+        <v>-0.02660631516206833</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.07233281828392406</v>
+        <v>-0.0974779713734345</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.01625004158412825</v>
+        <v>0.07255416195614338</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.006410697439343241</v>
+        <v>-0.00166481132365308</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.009991464683040772</v>
+        <v>-0.02143477387932599</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0117035573966711</v>
+        <v>0.04062153230752507</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.03400145871863834</v>
+        <v>-0.03925011179581708</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
@@ -6061,28 +6061,28 @@
         <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.001742342230571659</v>
+        <v>0.00914928195777647</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.002632620354687212</v>
+        <v>0.08788678793494081</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.003404350071809533</v>
+        <v>-0.01157723687015044</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
         <v>0</v>
@@ -6091,31 +6091,31 @@
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.01634329917391489</v>
+        <v>-0.07796487328060303</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.03699785307823184</v>
+        <v>0.03672524783598674</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF10" t="n">
         <v>0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,22 +6123,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3860685444695524</v>
+        <v>0.3647806793238299</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1141690800741555</v>
+        <v>-0.172036741715225</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.08271188432472305</v>
+        <v>0.01968429395090859</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
@@ -6150,22 +6150,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1829355616396811</v>
+        <v>0.2183298321620929</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.01446054530959619</v>
+        <v>-0.02217985210314379</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.04453142952883181</v>
+        <v>-0.002924705141801217</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6174,52 +6174,52 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1369772785662917</v>
+        <v>0.1016377250136189</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.02982205587082784</v>
+        <v>-0.02922826636402784</v>
       </c>
       <c r="W11" t="n">
-        <v>0.07347206322869854</v>
+        <v>-0.0691903113895815</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1260752604204138</v>
+        <v>-0.06636456577642461</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.04687873967860352</v>
+        <v>-0.173719828905508</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.03123882427387175</v>
+        <v>-0.0373524129183398</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
@@ -6228,19 +6228,19 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0517373757069514</v>
+        <v>0.1479810468036685</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.04693577510272039</v>
+        <v>-0.07966742889036647</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.02873920170596778</v>
+        <v>0.1138387768089732</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -6258,16 +6258,16 @@
         <v>-0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.4352448661264277</v>
+        <v>0.3695804843578664</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.003029365963111259</v>
+        <v>-0.152308901954658</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.1354190088360794</v>
+        <v>-0.1137689097679482</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
@@ -6279,22 +6279,22 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.02836527991567364</v>
+        <v>-0.01617406426559779</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.03404178528994286</v>
+        <v>-0.02923407922887424</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1253338311084696</v>
+        <v>-0.02218312207148299</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6303,7 +6303,7 @@
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
@@ -6312,22 +6312,22 @@
         <v>-0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.01864119223171074</v>
+        <v>-0.03116865778580338</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.04445658946713062</v>
+        <v>0.03884501496101608</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.05145281084716107</v>
+        <v>0.02711383900795365</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6339,49 +6339,49 @@
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.2604690935085517</v>
+        <v>0.327082976889236</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0.02231307279963652</v>
+        <v>-0.1146176438750104</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.07943533834213067</v>
+        <v>-0.01424526978808908</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.09827690266432829</v>
+        <v>-0.1396795763294643</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.02618285090985644</v>
+        <v>0.1470726399942006</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.02315152757546453</v>
+        <v>-0.04254836521647105</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,19 +6393,19 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.05345134043065182</v>
+        <v>-0.1298057512778343</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.07476594241106028</v>
+        <v>0.2248686083792075</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.167076016087498</v>
+        <v>0.02927684884562921</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
@@ -6420,22 +6420,22 @@
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.09150580622032395</v>
+        <v>-0.1285504083555058</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.03576284586004064</v>
+        <v>0.1408212952413083</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.01998796279913451</v>
+        <v>-0.02884671728370796</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
@@ -6444,25 +6444,25 @@
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.04256947303042163</v>
+        <v>-0.03811654224551935</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.01581421298383295</v>
+        <v>0.01736056773571083</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0004951969159955818</v>
+        <v>0.005380772385159763</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL11" t="n">
         <v>0</v>
@@ -6471,22 +6471,22 @@
         <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.05204242744462474</v>
+        <v>-0.07924915251009387</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0.005463698325473166</v>
+        <v>0.06638603440898624</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.06204460443714819</v>
+        <v>-0.01112876349694857</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6501,76 +6501,76 @@
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.08895742217609767</v>
+        <v>-0.005933609110331424</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.0204191241031179</v>
+        <v>-0.09247220723306046</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.006132100995516686</v>
+        <v>0.1089573596793195</v>
       </c>
       <c r="EB11" t="n">
         <v>0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.06172239568230441</v>
+        <v>-0.08750035412337751</v>
       </c>
       <c r="EH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.03635916135260377</v>
+        <v>0.1098907892894518</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.03997454528862483</v>
+        <v>0.0115433616085429</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.07627387971790586</v>
+        <v>-0.08446253302355194</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0206473654388265</v>
+        <v>0.06189068000717168</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.03062252082218282</v>
+        <v>-0.03677841590866018</v>
       </c>
       <c r="ET11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
@@ -6579,25 +6579,25 @@
         <v>-0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1025882726777533</v>
+        <v>-0.1546360374439853</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.04450534965843048</v>
+        <v>0.161990290820082</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.02725858841128379</v>
+        <v>-0.05172216921175717</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
@@ -6609,16 +6609,16 @@
         <v>-0</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.007373691659527414</v>
+        <v>-0.1230854776103581</v>
       </c>
       <c r="FI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.06288626401431556</v>
+        <v>0.09742313101848125</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.04604291415433229</v>
+        <v>-0.004779892956332153</v>
       </c>
       <c r="FL11" t="n">
         <v>-0</v>
@@ -6627,64 +6627,64 @@
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
         <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.01410257397447073</v>
+        <v>-0.01614694594528322</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
       </c>
       <c r="FS11" t="n">
-        <v>-0.1281988544453152</v>
+        <v>-0.168954940891126</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.02382377109969946</v>
+        <v>-0.02410282736933757</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.04158371759998803</v>
+        <v>-0.1131176495357851</v>
       </c>
       <c r="GA11" t="n">
         <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0.04610191740933486</v>
+        <v>0.08896809644111335</v>
       </c>
       <c r="GC11" t="n">
         <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -7258,22 +7258,22 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1052658734163721</v>
+        <v>0.627422820536647</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.04320202057340328</v>
+        <v>0.06061191564797961</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.05905002278961895</v>
+        <v>-0.3559869063142942</v>
       </c>
       <c r="G13" t="n">
         <v>-0</v>
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.04295118699287189</v>
+        <v>0.4848470099800309</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,13 +7297,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.02626478918343891</v>
+        <v>-0.07477875402112276</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.01779210163083662</v>
+        <v>-0.1248566387190366</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>-0</v>
@@ -7312,10 +7312,10 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.004315201574558581</v>
+        <v>0.1865836190134013</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -7324,16 +7324,16 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.02118477643181161</v>
+        <v>-0.1508150897546938</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02208182202543177</v>
+        <v>-0.054449992586172</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>-0</v>
@@ -7342,34 +7342,34 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.02178893815435579</v>
+        <v>-0.02451221587952385</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.02255643972430705</v>
+        <v>-0.3043818300567229</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.008955529374286314</v>
+        <v>-0.08725303996372012</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI13" t="n">
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01934415261992584</v>
+        <v>0.2047296173217211</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.01134245279903199</v>
+        <v>0.05375847318474691</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.02047164354368227</v>
+        <v>-0.18902297130363</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,22 +7393,22 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.08397229367139974</v>
+        <v>0.8549474041771488</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.03965968528460088</v>
+        <v>-0.2276815909294671</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.0307696123454659</v>
+        <v>-0.3443997222646378</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -7417,13 +7417,13 @@
         <v>-0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.03177258358605593</v>
+        <v>-0.06715582659037572</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,13 +7432,13 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.01930709527244431</v>
+        <v>-0.06485595659530104</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.01243948089378175</v>
+        <v>-0.06604753806436144</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
         <v>-0</v>
@@ -7447,37 +7447,37 @@
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.04010860812152438</v>
+        <v>0.0822693464709838</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.02954463615503292</v>
+        <v>0.1436962341524636</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01416156279207613</v>
+        <v>0.07772264146023329</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.04674285588966193</v>
+        <v>0.5563287333754479</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,40 +7486,40 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.01788130102593049</v>
+        <v>-0.07118081701521775</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.002134030280392688</v>
+        <v>-0.2323851639056316</v>
       </c>
       <c r="CA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB13" t="n">
         <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.01621965963627819</v>
+        <v>-0.2479423257840932</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.005475792416234756</v>
+        <v>-0.02800688302190992</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.01726675697218584</v>
+        <v>0.1608544468760856</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7531,7 +7531,7 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.005136498689521495</v>
+        <v>-0.3206695496005732</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
@@ -7540,13 +7540,13 @@
         <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.002702375558682941</v>
+        <v>0.1436771340074288</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.02753638282070571</v>
+        <v>0.1762073625745528</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
         <v>0</v>
@@ -7555,25 +7555,25 @@
         <v>0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.0112676657924886</v>
+        <v>-0.2196143630494782</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.008010826526126556</v>
+        <v>-0.0466529040804157</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.022009830323133</v>
+        <v>0.1646349066419909</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
@@ -7582,76 +7582,76 @@
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.004415211012725574</v>
+        <v>-0.04056075903832509</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.02306287208739509</v>
+        <v>-0.2390961412322847</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.00406529454022137</v>
+        <v>0.005237428461781487</v>
       </c>
       <c r="DK13" t="n">
         <v>0</v>
       </c>
       <c r="DL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.01511276425078155</v>
+        <v>-0.06403660509094541</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0104815703175914</v>
+        <v>-0.05251297355714121</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.01640995735574316</v>
+        <v>0.02654311202393523</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.001985719039636225</v>
+        <v>0.1552989774217814</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.02253200220825065</v>
+        <v>-0.04428079943792719</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.01452478347826923</v>
+        <v>0.05495848003892043</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
@@ -7663,10 +7663,10 @@
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.009558445313801806</v>
+        <v>-0.0548734780467573</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,13 +7675,13 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.005821113327950961</v>
+        <v>-0.1350478032104411</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.01807824704006479</v>
+        <v>0.06551998943514274</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>0</v>
@@ -7690,52 +7690,52 @@
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.003430035122489143</v>
+        <v>-0.1124493129546077</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.01151076542301022</v>
+        <v>-0.1804588040648966</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01703347142483065</v>
+        <v>0.1325432674203112</v>
       </c>
       <c r="EU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.007987245776195473</v>
+        <v>-0.2611165978457194</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.005474481293517712</v>
+        <v>-0.07421597977614532</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.02218428055851368</v>
+        <v>0.1393396736848286</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
@@ -7744,82 +7744,82 @@
         <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.0161118348492827</v>
+        <v>-0.2070471483929382</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.03139741915767542</v>
+        <v>0.08820371317209454</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.02060621513307019</v>
+        <v>0.2355773998782035</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.002414092888160417</v>
+        <v>-0.02774485721425285</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.00048274181441153</v>
+        <v>0.0007724081856934323</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.008386938207461912</v>
+        <v>0.1548384933794067</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.01601264112464079</v>
+        <v>-0.1212523038078352</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.01796211548304342</v>
+        <v>0.04147103644037487</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
@@ -7827,28 +7827,28 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.08973733290996719</v>
+        <v>0.2077414505562488</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D14" t="n">
         <v>-0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.04363036533815026</v>
+        <v>0.01466234705374211</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.02156490498913307</v>
+        <v>-0.1077644325869491</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -7857,34 +7857,34 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03875571495573658</v>
+        <v>0.1794941332711215</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.03113179646541618</v>
+        <v>-0.02753071641080561</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.006479027623837866</v>
+        <v>-0.04495021081227519</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.006638853685983463</v>
+        <v>0.06180007958870848</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
@@ -7893,25 +7893,25 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.006616592756181581</v>
+        <v>-0.0558993875343902</v>
       </c>
       <c r="X14" t="n">
-        <v>0.01804225124850013</v>
+        <v>-0.02169353517665368</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB14" t="n">
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.01810194689673993</v>
+        <v>-0.03144323551534938</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -7920,25 +7920,25 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.02277404962828885</v>
+        <v>-0.1064793166329098</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.007477851005114849</v>
+        <v>-0.04613413275717124</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01467252895541128</v>
+        <v>0.06097964293644918</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
@@ -7947,37 +7947,37 @@
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.01457688889906194</v>
+        <v>0.01991828404009555</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.01261926141194078</v>
+        <v>-0.07216822196090436</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.07458258276590379</v>
+        <v>0.2432388761723343</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.02270858578158457</v>
+        <v>-0.1050297328403207</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.005921112505210411</v>
+        <v>-0.09223632430093449</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.02902540495401127</v>
+        <v>-0.01399390515758598</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -8001,37 +8001,37 @@
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.02440380830372408</v>
+        <v>-0.02071822565696174</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.01810430359439813</v>
+        <v>-0.04481183372135537</v>
       </c>
       <c r="BI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.04438539492627638</v>
+        <v>0.02026315752943795</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.02128943147858666</v>
+        <v>0.0699021580394064</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.01175582963469083</v>
+        <v>0.05807575369095936</v>
       </c>
       <c r="BR14" t="n">
         <v>-0</v>
@@ -8040,13 +8040,13 @@
         <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
         <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.03760482512473504</v>
+        <v>0.1619083268834182</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
@@ -8055,16 +8055,16 @@
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.009207733777462635</v>
+        <v>-0.03846608167488708</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.01177033560236127</v>
+        <v>-0.07636058453363764</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
         <v>-0</v>
@@ -8073,22 +8073,22 @@
         <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.01113963544823329</v>
+        <v>-0.06851210580353395</v>
       </c>
       <c r="CF14" t="n">
         <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.008540381151450074</v>
+        <v>0.002226543794065762</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.009504973902215511</v>
+        <v>0.06562853534023264</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
@@ -8100,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.007565671789103549</v>
+        <v>-0.07212853004235267</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
@@ -8109,13 +8109,13 @@
         <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.00478063190907632</v>
+        <v>0.1004584927622055</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.01170301908861326</v>
+        <v>0.03650349465188414</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
         <v>-0</v>
@@ -8127,25 +8127,25 @@
         <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.006111028065611183</v>
+        <v>-0.06248877815009718</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.007956574682539366</v>
+        <v>-0.003929736350940091</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.01165319662273927</v>
+        <v>0.06837923266734859</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
         <v>0</v>
@@ -8154,19 +8154,19 @@
         <v>-0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.008646543992966443</v>
+        <v>-0.03093544367386237</v>
       </c>
       <c r="DG14" t="n">
         <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.000661436020803211</v>
+        <v>-0.01243639979336099</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.003792270102109945</v>
+        <v>-0.01681630782781365</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8175,31 +8175,31 @@
         <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.01474252436542887</v>
+        <v>-0.02629908806474939</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.01933505821069114</v>
+        <v>-0.01482057690703066</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0.02131939216751958</v>
+        <v>-0.02146890654326647</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>-0</v>
@@ -8208,25 +8208,25 @@
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.0003051787991176317</v>
+        <v>0.03102927730278724</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.03126446484648008</v>
+        <v>-0.01044282629403498</v>
       </c>
       <c r="EB14" t="n">
-        <v>-0.02569133796986356</v>
+        <v>0.02663036916940175</v>
       </c>
       <c r="EC14" t="n">
         <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
         <v>-0</v>
@@ -8235,79 +8235,79 @@
         <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.004783702941119086</v>
+        <v>-0.02033096619267932</v>
       </c>
       <c r="EH14" t="n">
         <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.006898259031043298</v>
+        <v>-0.02586847692215741</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.0016330287825996</v>
+        <v>0.03588493470202741</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.004532262027226124</v>
+        <v>-0.0379261295103732</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.0005377438406086963</v>
+        <v>-0.02783907988881224</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.01839370892917774</v>
+        <v>0.04457929896783316</v>
       </c>
       <c r="EU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
         <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.004578271558871831</v>
+        <v>-0.07014806052570631</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.007737370836684438</v>
+        <v>-0.008723343313503471</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.01527916163317275</v>
+        <v>0.05111681997350929</v>
       </c>
       <c r="FD14" t="n">
         <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
         <v>-0</v>
@@ -8316,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.007607065827906051</v>
+        <v>-0.062732692020456</v>
       </c>
       <c r="FI14" t="n">
         <v>0</v>
@@ -8325,67 +8325,67 @@
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.03354914501259099</v>
+        <v>0.02253889683855139</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.01303743320966156</v>
+        <v>0.04711148695033097</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.002179299737852478</v>
+        <v>-0.01556740577559344</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.000401249693616723</v>
+        <v>-0.0007360968758035229</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.003348842198980361</v>
+        <v>0.0483029259662929</v>
       </c>
       <c r="FV14" t="n">
         <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.02228688270709073</v>
+        <v>-0.04257255475824707</v>
       </c>
       <c r="GA14" t="n">
         <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0.01637251541976336</v>
+        <v>0.04395152204113223</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
         <v>0</v>
@@ -8968,127 +8968,127 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.3187051246916599</v>
+        <v>0.3551459068231119</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1489492520515811</v>
+        <v>-0.06624780114624799</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.09002751817248469</v>
+        <v>0.01098429745012845</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0622754085585477</v>
+        <v>-0.1016867037361101</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1992021633405539</v>
+        <v>0.3409251365716396</v>
       </c>
       <c r="L16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1100223130379771</v>
+        <v>-0.1032063220192036</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.06384690876651669</v>
+        <v>-0.06126922043566328</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.03777947866233954</v>
+        <v>-0.03776431422260999</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.06748234503628472</v>
+        <v>0.04734494179420583</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.01254594909241052</v>
+        <v>-0.08232009950528989</v>
       </c>
       <c r="W16" t="n">
-        <v>0.05182215268681091</v>
+        <v>-0.06073201395036021</v>
       </c>
       <c r="X16" t="n">
-        <v>0.04903665508515107</v>
+        <v>-0.03605285815306809</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.05591451940330632</v>
+        <v>-0.02133804096339007</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.04098066803660044</v>
+        <v>-0.1560318573565459</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.0113363782505748</v>
+        <v>-0.1148470254943638</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.01064786618755916</v>
+        <v>-0.04483845874131912</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0004988108534246238</v>
+        <v>0.1068143413943105</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.02780742572324407</v>
+        <v>-0.05825390522548553</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.03672815432272445</v>
+        <v>0.05439081277967019</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.03421535914898376</v>
+        <v>-0.08972461437830465</v>
       </c>
       <c r="AQ16" t="n">
         <v>-0</v>
@@ -9097,25 +9097,25 @@
         <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.3203659829527116</v>
+        <v>0.3335868263825847</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0.0235898126052109</v>
+        <v>-0.009629259157114704</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.02984768583685589</v>
+        <v>-0.08780535925609508</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.02106020949174865</v>
+        <v>-0.09812328642952726</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -9127,103 +9127,103 @@
         <v>-0</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>-0.001072429440116345</v>
+        <v>-0.01140236750930894</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>-0.02268530580535243</v>
+        <v>-0.06695445276446872</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1044271899895412</v>
+        <v>-0.05139082285314105</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.0501200693083438</v>
+        <v>-0.0193104478582178</v>
       </c>
       <c r="BI16" t="n">
         <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="n">
         <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.0592966882250069</v>
+        <v>0.02219673109581477</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.06457274857217001</v>
+        <v>0.002232439171185603</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.06362005606816112</v>
+        <v>0.08692222162543835</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.01862661953836153</v>
+        <v>0.01729389730064205</v>
       </c>
       <c r="BR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.152904167159655</v>
+        <v>0.2021413850493318</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.03566426065558426</v>
+        <v>-0.03783706356007563</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.009301953566094579</v>
+        <v>-0.02168645206373425</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.03284267381300353</v>
+        <v>-0.08911401918887189</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
         <v>-0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.061904795409631</v>
+        <v>-0.09791737837251817</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.01143126725340684</v>
+        <v>0.03225610680804188</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.004601576058983013</v>
+        <v>0.01974887851725612</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.03282588123079866</v>
+        <v>0.0362721956170256</v>
       </c>
       <c r="CJ16" t="n">
         <v>-0</v>
@@ -9232,28 +9232,28 @@
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.02433470009147189</v>
+        <v>-0.1016975543828742</v>
       </c>
       <c r="CO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0.09528500233630727</v>
+        <v>0.08915633568965595</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.06538539023569021</v>
+        <v>0.1217066319068705</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.07160432678532314</v>
+        <v>0.08301250285341864</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
         <v>-0</v>
@@ -9262,22 +9262,22 @@
         <v>0</v>
       </c>
       <c r="CV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.05000253652223097</v>
+        <v>-0.09174127876333839</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.03351915909049587</v>
+        <v>0.02623950052228598</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.006271334416042406</v>
+        <v>0.01432238616037525</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.04319125901262801</v>
+        <v>0.03659182256535285</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
@@ -9292,46 +9292,46 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.001289946644931425</v>
+        <v>-0.02671024991865038</v>
       </c>
       <c r="DG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.0591172678738161</v>
+        <v>-0.04319015153530167</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.004797224275910277</v>
+        <v>0.1105160589223386</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.005229672910767832</v>
+        <v>-0.009201923717437098</v>
       </c>
       <c r="DK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
         <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.0254965042945452</v>
+        <v>-0.08322142236751776</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.05324006702549526</v>
+        <v>0.03760436146061279</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.003712847301586662</v>
+        <v>-0.007618156034576174</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.008459506739143901</v>
+        <v>0.005632129299275784</v>
       </c>
       <c r="DT16" t="n">
         <v>0</v>
@@ -9340,196 +9340,196 @@
         <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.01337753817993134</v>
+        <v>0.06467366230099063</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.004357915243516064</v>
+        <v>0.008505927472670033</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.05459072035472773</v>
+        <v>-0.00783106266820404</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.007400929234524437</v>
+        <v>0.02133215047088441</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
         <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.08162364597873287</v>
+        <v>-0.05904384290557171</v>
       </c>
       <c r="EH16" t="n">
         <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.05743983815859426</v>
+        <v>0.04834120355707774</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.04949568264106391</v>
+        <v>0.02638423161580142</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.006716332308729729</v>
+        <v>-0.001698439665190165</v>
       </c>
       <c r="EL16" t="n">
         <v>-0</v>
       </c>
       <c r="EM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.03908186418205387</v>
+        <v>-0.02245930463353922</v>
       </c>
       <c r="EQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.003316639717130403</v>
+        <v>0.01060469725224102</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.02262352136749712</v>
+        <v>0.006178462308005487</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.06565069416797123</v>
+        <v>0.08030112938705838</v>
       </c>
       <c r="EU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.04613182958976267</v>
+        <v>-0.1071331813787448</v>
       </c>
       <c r="EZ16" t="n">
         <v>-0</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.0176625289103931</v>
+        <v>0.0227492879967365</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.006520506445012923</v>
+        <v>0.0106235942148288</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.03459328209596833</v>
+        <v>0.02900336782100998</v>
       </c>
       <c r="FD16" t="n">
         <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.03965977904545533</v>
+        <v>-0.03317414728052074</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.05704261889428647</v>
+        <v>0.03266659876532933</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.00603480969582025</v>
+        <v>0.003943278395733587</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0.002910244989505028</v>
+        <v>0.02763113854297916</v>
       </c>
       <c r="FM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.01095635583721517</v>
+        <v>-0.09027110150367833</v>
       </c>
       <c r="FR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.01201145400328422</v>
+        <v>0.16897490766619</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.006632200171119691</v>
+        <v>-0.009100134241440631</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.01082056739895922</v>
+        <v>0.1117377186749091</v>
       </c>
       <c r="FV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.006014361215978115</v>
+        <v>-0.09272021558676033</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0.04180194767149894</v>
+        <v>-0.07432465772898592</v>
       </c>
       <c r="GC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.01483391711139229</v>
+        <v>0.0006097985196584007</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1507833027504652</v>
+        <v>0.5180481033177419</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -10115,10 +10115,10 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.07467417371888677</v>
+        <v>0.06147994282379924</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.06653412378738222</v>
+        <v>-0.209093573008236</v>
       </c>
       <c r="G18" t="n">
         <v>-0</v>
@@ -10133,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1094409410262945</v>
+        <v>0.643979264321317</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -10142,13 +10142,13 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.05496168156868961</v>
+        <v>-0.07181431967098559</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.03744628605783663</v>
+        <v>-0.1110065846545526</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-0</v>
@@ -10157,10 +10157,10 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.01463975394307872</v>
+        <v>0.0825688503498333</v>
       </c>
       <c r="U18" t="n">
         <v>-0</v>
@@ -10169,25 +10169,25 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.02316929884272893</v>
+        <v>-0.06198560141531508</v>
       </c>
       <c r="X18" t="n">
-        <v>0.01937607019138276</v>
+        <v>0.04076128392298476</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.02767508389773804</v>
+        <v>0.01791058539452526</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -10196,13 +10196,13 @@
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.02618960847411302</v>
+        <v>-0.1630568678752857</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.001143404702909475</v>
+        <v>-0.07516107783948249</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>-0</v>
@@ -10214,61 +10214,61 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.02473386421884555</v>
+        <v>0.07902847171312587</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.01232726247392478</v>
+        <v>0.0130707113805475</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.03229264730419328</v>
+        <v>-0.1534995418770378</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.09588355770063949</v>
+        <v>0.4745401595134287</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.0324299892848357</v>
+        <v>-0.223957936144948</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.03545442588276625</v>
+        <v>-0.1342807609504265</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC18" t="n">
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.02983601455468899</v>
+        <v>0.006898298446222749</v>
       </c>
       <c r="BE18" t="n">
         <v>0</v>
@@ -10277,52 +10277,52 @@
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.04119053948865173</v>
+        <v>-0.05945762377877578</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.005366368448716368</v>
+        <v>-0.1059214426079688</v>
       </c>
       <c r="BI18" t="n">
         <v>-0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
         <v>-0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.04251893030799123</v>
+        <v>0.0813423821057223</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.02635054973591057</v>
+        <v>0.09997891046611389</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.01899540148185775</v>
+        <v>-0.001708946803609338</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
         <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.05881871221633909</v>
+        <v>0.2973278672917199</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
@@ -10331,37 +10331,37 @@
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.02185609697105313</v>
+        <v>-0.08465652771461853</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.005844403953537277</v>
+        <v>-0.08813786074675257</v>
       </c>
       <c r="CA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC18" t="n">
         <v>-0</v>
       </c>
       <c r="CD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.0190709811779678</v>
+        <v>-0.1509462880393314</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.007675109732017718</v>
+        <v>0.03739010556203573</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.01547887986884864</v>
+        <v>0.06568594532480369</v>
       </c>
       <c r="CJ18" t="n">
         <v>-0</v>
@@ -10370,13 +10370,13 @@
         <v>0</v>
       </c>
       <c r="CL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM18" t="n">
         <v>0</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.001084650870710764</v>
+        <v>-0.2408495160815819</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
@@ -10385,13 +10385,13 @@
         <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>-0.01264115901661678</v>
+        <v>0.2585020257848481</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.02859485132024796</v>
+        <v>0.1242683961836985</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
         <v>-0</v>
@@ -10403,19 +10403,19 @@
         <v>-0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.01511049122574344</v>
+        <v>-0.1537191133321979</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.005730089539273469</v>
+        <v>-0.005172126432719299</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.02210293220111836</v>
+        <v>0.05930396982316762</v>
       </c>
       <c r="DB18" t="n">
         <v>0</v>
@@ -10430,19 +10430,19 @@
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.001469904406129279</v>
+        <v>0.002126596608247948</v>
       </c>
       <c r="DG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.01673648575857769</v>
+        <v>-0.0605692745775366</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.001094121716201831</v>
+        <v>0.01037031573494669</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
@@ -10454,22 +10454,22 @@
         <v>0</v>
       </c>
       <c r="DN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.01826452097067918</v>
+        <v>-0.08112097273615204</v>
       </c>
       <c r="DP18" t="n">
         <v>-0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.02629721780048799</v>
+        <v>-0.03961490702160498</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.0307774575120966</v>
+        <v>-0.005410691007561073</v>
       </c>
       <c r="DT18" t="n">
         <v>-0</v>
@@ -10478,25 +10478,25 @@
         <v>-0</v>
       </c>
       <c r="DV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW18" t="n">
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.0001847505999447847</v>
+        <v>0.05379098968229609</v>
       </c>
       <c r="DY18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ18" t="n">
         <v>0</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.02619775491746928</v>
+        <v>-0.05268054833391958</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0.01772487370828326</v>
+        <v>-0.05592312843756012</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
@@ -10511,76 +10511,76 @@
         <v>0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.01085945387854833</v>
+        <v>-0.03698881960208775</v>
       </c>
       <c r="EH18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.01774826038541308</v>
+        <v>-0.05929001476202606</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.002849313117947491</v>
+        <v>0.02433424203969798</v>
       </c>
       <c r="EL18" t="n">
         <v>-0</v>
       </c>
       <c r="EM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.004220568307922598</v>
+        <v>-0.0693866785405625</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES18" t="n">
-        <v>-0.01063190175657089</v>
+        <v>-0.03800474644069021</v>
       </c>
       <c r="ET18" t="n">
-        <v>-0.02310275477909809</v>
+        <v>-0.09810446638067608</v>
       </c>
       <c r="EU18" t="n">
         <v>-0</v>
       </c>
       <c r="EV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.01192516502674933</v>
+        <v>-0.163350001726733</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
         <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.003181824698183061</v>
+        <v>0.007860646053425525</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.0222865266786864</v>
+        <v>0.05230941185838079</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
@@ -10589,37 +10589,37 @@
         <v>-0</v>
       </c>
       <c r="FG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.01230257420660831</v>
+        <v>-0.1325234891259381</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>-0.0402899169604589</v>
+        <v>0.07938080095738352</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.01520103024520643</v>
+        <v>0.1221670086556265</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
         <v>0</v>
       </c>
       <c r="FP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>-0.002409298342595829</v>
+        <v>-0.1169374370399837</v>
       </c>
       <c r="FR18" t="n">
         <v>-0</v>
@@ -10628,37 +10628,37 @@
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.0003948844006530285</v>
+        <v>0.01811202582686371</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.01479161714737616</v>
+        <v>0.07554990158658766</v>
       </c>
       <c r="FV18" t="n">
         <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.01431095049276781</v>
+        <v>-0.07945850591444292</v>
       </c>
       <c r="GA18" t="n">
         <v>0</v>
       </c>
       <c r="GB18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.0228038178607163</v>
+        <v>-0.04679376899199307</v>
       </c>
       <c r="GE18" t="n">
         <v>-0</v>
